--- a/FinanceDataMigration/src/main/resources/migration-templates/FUND.xlsx
+++ b/FinanceDataMigration/src/main/resources/migration-templates/FUND.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t xml:space="preserve">Fund Master</t>
   </si>
@@ -30,7 +30,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">ULB Name </t>
@@ -87,10 +86,13 @@
     <t xml:space="preserve">Gurugram Municipal Corporation</t>
   </si>
   <si>
-    <t xml:space="preserve">Municipal Fund</t>
+    <t>TESTING</t>
   </si>
   <si>
     <t xml:space="preserve">MC Fund</t>
+  </si>
+  <si>
+    <t>Hello</t>
   </si>
 </sst>
 </file>
@@ -107,35 +109,32 @@
     <font>
       <b/>
       <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FFC9211E"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -178,22 +177,22 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -734,7 +733,7 @@
     <col customWidth="1" min="6" max="26" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -869,10 +868,18 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="8"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -28761,32 +28768,12 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <dataValidations count="3" disablePrompts="0">
-    <dataValidation sqref="B4:B1000" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E4:E1000" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>Fund!$C$4:$C$1000</formula1>
-    </dataValidation>
-    <dataValidation sqref="D4:D1000" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$D$2:$D$1000</formula1>
-    </dataValidation>
+  <dataValidations count="1" disablePrompts="0">
+    <dataValidation sqref="1:1048576" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="0" copies="1"/>
   <headerFooter/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{AA7BDD3F-D6FE-4D6F-9199-8FBBDD878F8B}" type="custom" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="1" showErrorMessage="1" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>COUNTIF($C$4:$C$1000,C4)=1</xm:f>
-          </x14:formula1>
-          <xm:sqref>C4:C1000</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>